--- a/artfynd/A 31670-2023 artfynd.xlsx
+++ b/artfynd/A 31670-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31670-2023 artfynd.xlsx
+++ b/artfynd/A 31670-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>104325396</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472108.8649782666</v>
+        <v>472109</v>
       </c>
       <c r="R4" t="n">
-        <v>6813966.923014824</v>
+        <v>6813967</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +984,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 31670-2023 artfynd.xlsx
+++ b/artfynd/A 31670-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>104325396</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
